--- a/old/_260816_230000_Black Friday.xlsx
+++ b/old/_260816_230000_Black Friday.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC083F9E-2358-42BE-B369-DD1A67DE4B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF65D0E-1811-474E-9389-79B75C841536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10950" yWindow="3000" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10470" yWindow="2250" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Dienstleistungsverkehr</t>
   </si>
@@ -49,13 +49,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> in Wahrheit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>weglenken</t>
-  </si>
-  <si>
     <t>basiert</t>
   </si>
   <si>
@@ -67,6 +60,10 @@
   </si>
   <si>
     <t>tummeln</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weglenken</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -563,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.08203125" customWidth="1"/>
@@ -593,41 +590,39 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-    </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C12" s="15"/>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C11" s="15"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C24" s="15"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C25" s="15"/>
@@ -642,56 +637,53 @@
       <c r="C28" s="15"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C29" s="15"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="22"/>
-      <c r="C30" s="21"/>
+      <c r="A29" s="22"/>
+      <c r="C29" s="21"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C31" s="15"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C32" s="15"/>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C33" s="15"/>
-    </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C40" s="17"/>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C39" s="17"/>
+    </row>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C44" s="14"/>
     </row>
     <row r="45" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C45" s="14"/>
-    </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C46" s="18"/>
-    </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C54" s="15"/>
-    </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C57" s="15"/>
-    </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C63" s="15"/>
+      <c r="C45" s="18"/>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C53" s="15"/>
+    </row>
+    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C56" s="15"/>
+    </row>
+    <row r="62" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C62" s="15"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C65" s="7"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C66" s="7"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C67" s="17"/>
+      <c r="C66" s="17"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C68" s="15"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C69" s="15"/>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C70" s="19"/>
+      <c r="C69" s="19"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C72" s="14"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C73" s="14"/>
+      <c r="C73" s="15"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C74" s="15"/>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="A74" t="s">
         <v>0</v>
       </c>
     </row>
